--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1525,31 +1525,31 @@
     <t>G15_60/SI01</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Pathologies chroniques stabilisées (SI)</t>
   </si>
   <si>
     <t>G15_60/SI02</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Oncologie et hémato-oncologie (SI)</t>
   </si>
   <si>
     <t>G15_60/SI03</t>
   </si>
   <si>
-    <t>Infirmier - Exerc. infirmier pratique avancée maladie rénale chroniq.,dialyse,transp. rénale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Maladie rénale chronique, dialyse, transplantation rénale (SI)</t>
   </si>
   <si>
     <t>G15_60/SI04</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée santé mentale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Psychiatrie et santé mentale (SI)</t>
   </si>
   <si>
     <t>G15_60/SI05</t>
   </si>
   <si>
-    <t>Infirmier - Exercice infirmier en pratique avancée urgences (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Urgences (SI)</t>
   </si>
   <si>
     <t>G15_60/SI06</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="833">
   <si>
     <t>Property</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260928120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2429,12 +2429,6 @@
   </si>
   <si>
     <t>Attaché de recherche clinique</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>Praticien A Diplôme Hors Union Européenne (PADHUE)</t>
   </si>
   <si>
     <t>365</t>
@@ -5535,7 +5529,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -6144,26 +6138,18 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>832</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>833</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -619,7 +619,7 @@
     <t>G15_10/SM76</t>
   </si>
   <si>
-    <t>Médecin - Anesthésie-réanimation option anesthésie-pédiatrique (SM)</t>
+    <t>Médecin - Anesthésie-réanimation option réanimation-pédiatrique (SM)</t>
   </si>
   <si>
     <t>G15_10/SM77</t>

--- a/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2026/ValueSet-JDV-J01-XdsAuthorSpecialty-CISIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="811">
   <si>
     <t>Property</t>
   </si>
@@ -2143,12 +2143,6 @@
     <t>Autre acteur mettant en oeuvre la méthode MAIA</t>
   </si>
   <si>
-    <t>312</t>
-  </si>
-  <si>
-    <t>Autre professionnel</t>
-  </si>
-  <si>
     <t>313</t>
   </si>
   <si>
@@ -2275,66 +2269,18 @@
     <t>Gestionnaire alertes et urgences sanitaires</t>
   </si>
   <si>
-    <t>336</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans l'accueil et l'orientation des personnes</t>
-  </si>
-  <si>
-    <t>337</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans la logistique</t>
-  </si>
-  <si>
     <t>338</t>
   </si>
   <si>
     <t>Autre professionnel intervenant dans l'hôtellerie et la restauration</t>
   </si>
   <si>
-    <t>339</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans la direction de la qualité, hygiène, sécurité et environnement</t>
-  </si>
-  <si>
     <t>340</t>
   </si>
   <si>
     <t>Autre professionnel intervenant dans la direction des systèmes d'information</t>
   </si>
   <si>
-    <t>341</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans la direction des finances et comptabilité</t>
-  </si>
-  <si>
-    <t>342</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans la direction de la communication</t>
-  </si>
-  <si>
-    <t>343</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans la direction des ressources humaines</t>
-  </si>
-  <si>
-    <t>344</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans la direction des affaires médicales</t>
-  </si>
-  <si>
-    <t>345</t>
-  </si>
-  <si>
-    <t>Autre professionnel intervenant dans le social, éducatif, psychologie et culturel</t>
-  </si>
-  <si>
     <t>346</t>
   </si>
   <si>
@@ -2353,12 +2299,6 @@
     <t>Etudiant - auxiliaire de puériculture</t>
   </si>
   <si>
-    <t>349</t>
-  </si>
-  <si>
-    <t>Etudiant - masseur-kinésithérapeute</t>
-  </si>
-  <si>
     <t>351</t>
   </si>
   <si>
@@ -2399,12 +2339,6 @@
   </si>
   <si>
     <t>Autre étudiant</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
-    <t>Directeur d'établissement</t>
   </si>
   <si>
     <t>360</t>
@@ -5529,7 +5463,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -6050,106 +5984,18 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>810</v>
+        <v>42</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>811</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>812</v>
+        <v>43</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s" s="2">
-        <v>822</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>824</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>826</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>828</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>830</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>832</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
